--- a/data/trans_camb/P16A10-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A10-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 4,27</t>
+          <t>-3,19; 3,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 2,87</t>
+          <t>-4,21; 2,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 3,92</t>
+          <t>-2,77; 4,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 5,93</t>
+          <t>-1,21; 6,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 4,56</t>
+          <t>-1,99; 4,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 3,53</t>
+          <t>-2,65; 3,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 3,7</t>
+          <t>-1,51; 3,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 2,57</t>
+          <t>-2,18; 2,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 2,66</t>
+          <t>-1,9; 2,8</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-55,16; 136,61</t>
+          <t>-51,18; 123,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-57,81; 100,01</t>
+          <t>-60,42; 84,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-43,92; 117,31</t>
+          <t>-41,09; 119,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,9; 355,23</t>
+          <t>-29,83; 366,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,34; 272,01</t>
+          <t>-44,43; 301,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,04; 212,32</t>
+          <t>-52,13; 187,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,32; 119,29</t>
+          <t>-27,66; 131,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,65; 83,27</t>
+          <t>-40,05; 89,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-32,98; 91,88</t>
+          <t>-33,02; 98,68</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 0,11</t>
+          <t>-5,75; 0,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 3,44</t>
+          <t>-3,23; 3,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 2,66</t>
+          <t>-3,83; 2,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 2,67</t>
+          <t>-2,8; 2,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 3,36</t>
+          <t>-2,45; 3,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 1,62</t>
+          <t>-3,04; 1,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,35</t>
+          <t>-3,49; 0,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 2,39</t>
+          <t>-1,98; 2,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 1,42</t>
+          <t>-2,51; 1,39</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-68,61; 4,38</t>
+          <t>-69,11; 5,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-35,98; 65,47</t>
+          <t>-37,89; 67,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,34; 56,88</t>
+          <t>-44,14; 49,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,68; 65,42</t>
+          <t>-42,42; 67,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,27; 87,7</t>
+          <t>-37,55; 88,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,18; 42,42</t>
+          <t>-44,73; 54,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,73; 7,85</t>
+          <t>-48,47; 16,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,03; 46,64</t>
+          <t>-29,05; 52,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-38,4; 29,89</t>
+          <t>-36,65; 28,36</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 5,67</t>
+          <t>-1,5; 5,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 4,13</t>
+          <t>-2,3; 4,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 4,64</t>
+          <t>-1,33; 5,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 4,79</t>
+          <t>-2,05; 5,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 0,55</t>
+          <t>-5,36; 0,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 4,98</t>
+          <t>-1,46; 5,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 4,56</t>
+          <t>-0,98; 4,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 1,62</t>
+          <t>-2,9; 1,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 3,95</t>
+          <t>-0,26; 4,06</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,04; 188,2</t>
+          <t>-30,92; 202,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,69; 149,48</t>
+          <t>-38,53; 158,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-28,21; 168,78</t>
+          <t>-24,33; 175,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-32,61; 138,0</t>
+          <t>-32,36; 154,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-80,12; 23,97</t>
+          <t>-79,12; 25,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 140,31</t>
+          <t>-20,67; 144,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 125,56</t>
+          <t>-16,73; 119,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-46,7; 45,89</t>
+          <t>-50,84; 41,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 119,79</t>
+          <t>-4,98; 118,6</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 6,94</t>
+          <t>0,07; 7,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 6,07</t>
+          <t>-0,18; 5,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 5,47</t>
+          <t>-0,66; 5,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 2,46</t>
+          <t>-4,4; 2,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 9,52</t>
+          <t>0,71; 8,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 1,2</t>
+          <t>-5,09; 0,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 3,48</t>
+          <t>-1,03; 3,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 6,49</t>
+          <t>1,25; 6,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,98</t>
+          <t>-2,61; 1,91</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,11; 286,91</t>
+          <t>-2,39; 264,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 229,16</t>
+          <t>-8,88; 220,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,32; 214,24</t>
+          <t>-15,36; 206,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-55,76; 61,29</t>
+          <t>-55,37; 60,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,76; 220,39</t>
+          <t>7,65; 211,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,49; 28,83</t>
+          <t>-66,13; 17,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,91; 88,61</t>
+          <t>-18,4; 91,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,08; 161,37</t>
+          <t>18,56; 155,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-39,83; 49,12</t>
+          <t>-42,55; 50,16</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 3,21</t>
+          <t>-6,98; 3,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 3,18</t>
+          <t>-6,8; 3,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,22; -0,79</t>
+          <t>-9,2; -0,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 5,76</t>
+          <t>-3,21; 5,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 3,27</t>
+          <t>-4,63; 3,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 2,35</t>
+          <t>-4,69; 2,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 2,9</t>
+          <t>-3,57; 3,06</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 1,69</t>
+          <t>-4,35; 1,94</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,35; -0,04</t>
+          <t>-5,38; 0,15</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-63,56; 70,86</t>
+          <t>-65,38; 68,37</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-66,9; 68,72</t>
+          <t>-64,95; 63,2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-81,25; -11,38</t>
+          <t>-80,18; -2,36</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-45,83; 197,61</t>
+          <t>-47,2; 217,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-68,76; 106,42</t>
+          <t>-66,29; 131,12</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-57,82; 89,98</t>
+          <t>-59,42; 88,01</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-47,1; 62,95</t>
+          <t>-44,58; 67,56</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-56,1; 37,69</t>
+          <t>-54,64; 45,16</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-62,47; -0,09</t>
+          <t>-62,73; 5,29</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 3,82</t>
+          <t>-4,35; 3,78</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 2,01</t>
+          <t>-5,5; 2,04</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 2,97</t>
+          <t>-4,27; 3,14</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 3,75</t>
+          <t>-4,85; 4,14</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 5,08</t>
+          <t>-3,99; 5,12</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 1,72</t>
+          <t>-5,36; 1,89</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 3,09</t>
+          <t>-2,9; 3,39</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 2,9</t>
+          <t>-3,55; 2,29</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 1,66</t>
+          <t>-3,8; 1,32</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-49,11; 88,5</t>
+          <t>-51,58; 87,75</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-68,24; 49,43</t>
+          <t>-67,57; 52,63</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-45,91; 70,16</t>
+          <t>-48,45; 77,4</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-53,96; 72,93</t>
+          <t>-53,4; 85,29</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-45,19; 106,43</t>
+          <t>-46,65; 108,94</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-56,41; 41,51</t>
+          <t>-56,54; 43,05</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-36,08; 64,1</t>
+          <t>-35,83; 66,7</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-42,59; 54,8</t>
+          <t>-43,33; 45,38</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-41,96; 32,8</t>
+          <t>-43,83; 27,24</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 4,68</t>
+          <t>-0,06; 4,59</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 3,48</t>
+          <t>-1,29; 3,56</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 3,38</t>
+          <t>-1,05; 3,51</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 0,9</t>
+          <t>-3,39; 1,08</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 1,02</t>
+          <t>-3,47; 1,11</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 1,66</t>
+          <t>-3,81; 1,83</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 2,14</t>
+          <t>-1,31; 2,08</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 1,68</t>
+          <t>-1,71; 1,73</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 1,84</t>
+          <t>-1,9; 2,06</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 150,39</t>
+          <t>-6,5; 147,19</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-25,43; 109,72</t>
+          <t>-24,79; 105,91</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-26,04; 104,15</t>
+          <t>-20,62; 118,46</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-56,15; 29,42</t>
+          <t>-56,1; 28,76</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-57,31; 31,63</t>
+          <t>-57,97; 32,56</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-60,9; 40,84</t>
+          <t>-60,88; 44,06</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-23,79; 56,33</t>
+          <t>-24,29; 55,03</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-32,75; 44,04</t>
+          <t>-32,85; 46,66</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-38,63; 48,09</t>
+          <t>-37,89; 52,95</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,86; -0,65</t>
+          <t>-4,84; -0,46</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,55</t>
+          <t>-1,47; 3,4</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 1,25</t>
+          <t>-4,6; 1,16</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 0,06</t>
+          <t>-4,33; -0,05</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 1,69</t>
+          <t>-3,12; 1,54</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 2,01</t>
+          <t>-1,94; 2,36</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,79; -0,84</t>
+          <t>-3,88; -0,84</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,86</t>
+          <t>-1,58; 1,94</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,1</t>
+          <t>-3,12; 1,1</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-68,13; -12,16</t>
+          <t>-68,97; -8,8</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-23,57; 82,68</t>
+          <t>-21,89; 75,3</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-67,96; 22,13</t>
+          <t>-66,9; 23,81</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-61,88; 3,07</t>
+          <t>-62,44; 1,44</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-43,43; 38,72</t>
+          <t>-44,12; 35,01</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-30,92; 48,01</t>
+          <t>-27,46; 55,94</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-58,49; -16,5</t>
+          <t>-59,03; -15,38</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 38,88</t>
+          <t>-24,72; 40,25</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-46,85; 20,81</t>
+          <t>-47,06; 20,76</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,01</t>
+          <t>-1,17; 1,04</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,62</t>
+          <t>-0,64; 1,59</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,06</t>
+          <t>-1,56; 1,07</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,53</t>
+          <t>-1,54; 0,61</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,17</t>
+          <t>-0,99; 1,26</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 0,57</t>
+          <t>-1,58; 0,57</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,46</t>
+          <t>-1,03; 0,46</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,16</t>
+          <t>-0,48; 1,11</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,59</t>
+          <t>-1,04; 0,64</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-20,75; 21,11</t>
+          <t>-19,8; 21,89</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 34,73</t>
+          <t>-10,95; 32,54</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-24,63; 21,54</t>
+          <t>-27,05; 21,93</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-26,84; 11,11</t>
+          <t>-26,0; 13,5</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-18,37; 23,83</t>
+          <t>-17,16; 26,76</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-28,83; 11,78</t>
+          <t>-27,0; 12,23</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 9,16</t>
+          <t>-18,15; 9,24</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 23,62</t>
+          <t>-8,42; 22,24</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 11,46</t>
+          <t>-18,23; 12,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A10-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A10-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,44</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 3,99</t>
+          <t>-3,77; 3,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 2,74</t>
+          <t>-4,19; 2,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 4,05</t>
+          <t>-2,85; 3,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 6,08</t>
+          <t>-1,31; 5,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 4,95</t>
+          <t>-2,57; 4,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 3,37</t>
+          <t>-3,22; 2,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 3,84</t>
+          <t>-1,57; 3,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 2,77</t>
+          <t>-2,16; 2,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 2,8</t>
+          <t>-1,97; 2,32</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-51,18; 123,06</t>
+          <t>-56,91; 108,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-60,42; 84,91</t>
+          <t>-60,6; 87,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-41,09; 119,41</t>
+          <t>-40,25; 114,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,83; 366,02</t>
+          <t>-37,15; 342,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,43; 301,82</t>
+          <t>-55,7; 240,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,13; 187,1</t>
+          <t>-59,64; 151,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,66; 131,4</t>
+          <t>-30,47; 116,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-40,05; 89,26</t>
+          <t>-40,47; 89,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-33,02; 98,68</t>
+          <t>-34,33; 79,73</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,47</t>
+          <t>-0,48</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,69</t>
+          <t>-0,78</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,57</t>
+          <t>-0,63</t>
         </is>
       </c>
     </row>
@@ -898,42 +898,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 3,43</t>
+          <t>-2,96; 3,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 2,54</t>
+          <t>-3,46; 2,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 2,46</t>
+          <t>-2,61; 2,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 3,08</t>
+          <t>-2,54; 3,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 1,73</t>
+          <t>-3,27; 1,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,8</t>
+          <t>-3,54; 0,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 2,43</t>
+          <t>-1,94; 2,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,39</t>
+          <t>-2,73; 1,4</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-7,07%</t>
+          <t>-7,14%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-13,17%</t>
+          <t>-14,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-9,59%</t>
+          <t>-10,61%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-69,11; 5,2</t>
+          <t>-67,64; 6,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-37,89; 67,58</t>
+          <t>-36,13; 72,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-44,14; 49,54</t>
+          <t>-43,73; 60,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-42,42; 67,18</t>
+          <t>-39,85; 74,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,55; 88,09</t>
+          <t>-39,44; 87,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,73; 54,03</t>
+          <t>-47,49; 45,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,47; 16,9</t>
+          <t>-49,77; 10,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,05; 52,82</t>
+          <t>-28,04; 48,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-36,65; 28,36</t>
+          <t>-38,04; 28,99</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,88</t>
+          <t>1,81</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,91</t>
+          <t>1,82</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,91</t>
+          <t>1,83</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 5,93</t>
+          <t>-1,51; 5,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 4,49</t>
+          <t>-2,36; 4,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 5,05</t>
+          <t>-1,45; 4,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 5,37</t>
+          <t>-2,15; 4,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 0,82</t>
+          <t>-5,66; 0,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 5,16</t>
+          <t>-1,43; 4,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 4,24</t>
+          <t>-0,87; 4,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 1,61</t>
+          <t>-2,59; 1,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,06</t>
+          <t>-0,53; 4,06</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>38,41%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-30,92; 202,48</t>
+          <t>-29,65; 200,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-38,53; 158,82</t>
+          <t>-40,59; 152,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-24,33; 175,61</t>
+          <t>-26,06; 179,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-32,36; 154,19</t>
+          <t>-35,37; 146,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-79,12; 25,63</t>
+          <t>-81,07; 26,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,67; 144,98</t>
+          <t>-21,69; 144,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 119,15</t>
+          <t>-15,4; 113,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,84; 41,33</t>
+          <t>-45,9; 53,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 118,6</t>
+          <t>-9,07; 114,3</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>1,85</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,97</t>
+          <t>-1,16</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,15</t>
+          <t>0,29</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 7,05</t>
+          <t>0,15; 7,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 5,91</t>
+          <t>-0,32; 6,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 5,4</t>
+          <t>-1,01; 4,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 2,55</t>
+          <t>-4,15; 2,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 8,94</t>
+          <t>0,37; 9,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 0,74</t>
+          <t>-4,09; 2,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,65</t>
+          <t>-1,15; 3,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,24</t>
+          <t>1,12; 6,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 1,91</t>
+          <t>-1,93; 2,45</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-33,44%</t>
+          <t>-19,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-3,03%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 264,47</t>
+          <t>-1,68; 264,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 220,99</t>
+          <t>-7,89; 233,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,36; 206,72</t>
+          <t>-19,85; 177,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-55,37; 60,7</t>
+          <t>-53,09; 64,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,65; 211,17</t>
+          <t>3,85; 220,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,13; 17,16</t>
+          <t>-53,65; 57,59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,4; 91,47</t>
+          <t>-18,94; 94,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,56; 155,83</t>
+          <t>15,04; 161,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-42,55; 50,16</t>
+          <t>-31,55; 64,11</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-4,46</t>
+          <t>-4,58</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>-0,85</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,48</t>
+          <t>-2,68</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 3,41</t>
+          <t>-6,82; 3,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 3,07</t>
+          <t>-6,92; 3,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,2; -0,66</t>
+          <t>-9,35; -1,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 5,59</t>
+          <t>-3,23; 5,7</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 3,36</t>
+          <t>-5,02; 3,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 2,37</t>
+          <t>-5,15; 2,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 3,06</t>
+          <t>-3,1; 3,18</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 1,94</t>
+          <t>-4,52; 1,85</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 0,15</t>
+          <t>-5,58; 0,05</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-56,6%</t>
+          <t>-58,17%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-12,31%</t>
+          <t>-17,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-38,71%</t>
+          <t>-41,77%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-65,38; 68,37</t>
+          <t>-65,26; 62,78</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-64,95; 63,2</t>
+          <t>-63,3; 64,76</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-80,18; -2,36</t>
+          <t>-81,01; -15,09</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-47,2; 217,72</t>
+          <t>-47,44; 204,02</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-66,29; 131,12</t>
+          <t>-71,25; 130,88</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-59,42; 88,01</t>
+          <t>-62,73; 85,57</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-44,58; 67,56</t>
+          <t>-42,02; 73,83</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-54,64; 45,16</t>
+          <t>-55,93; 39,1</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-62,73; 5,29</t>
+          <t>-66,15; -0,68</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,38</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-1,53</t>
+          <t>-1,43</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,89</t>
+          <t>-0,91</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 3,78</t>
+          <t>-3,72; 4,09</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 2,04</t>
+          <t>-5,29; 2,42</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 3,14</t>
+          <t>-4,03; 3,13</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 4,14</t>
+          <t>-4,64; 4,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 5,12</t>
+          <t>-4,1; 5,38</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 1,89</t>
+          <t>-5,19; 1,72</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 3,39</t>
+          <t>-3,03; 2,84</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 2,29</t>
+          <t>-3,42; 3,04</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 1,32</t>
+          <t>-3,49; 1,33</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-4,2%</t>
+          <t>-5,96%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-22,13%</t>
+          <t>-20,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-13,4%</t>
+          <t>-13,61%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-51,58; 87,75</t>
+          <t>-46,93; 100,63</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-67,57; 52,63</t>
+          <t>-64,31; 66,06</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-48,45; 77,4</t>
+          <t>-46,24; 77,41</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-53,4; 85,29</t>
+          <t>-50,67; 83,03</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-46,65; 108,94</t>
+          <t>-46,31; 111,64</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-56,54; 43,05</t>
+          <t>-54,26; 38,79</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-35,83; 66,7</t>
+          <t>-36,75; 58,59</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-43,33; 45,38</t>
+          <t>-41,66; 58,06</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-43,83; 27,24</t>
+          <t>-40,83; 27,84</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,21</t>
+          <t>1,55</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>1,4</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 4,59</t>
+          <t>-0,25; 4,81</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,56</t>
+          <t>-1,27; 3,5</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 3,51</t>
+          <t>-0,91; 3,67</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 1,08</t>
+          <t>-3,71; 0,86</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 1,11</t>
+          <t>-3,29; 1,2</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 1,83</t>
+          <t>-1,15; 3,35</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,08</t>
+          <t>-1,08; 2,07</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,73</t>
+          <t>-1,61; 1,58</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 2,06</t>
+          <t>-0,26; 2,84</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-10,89%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>30,7%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 147,19</t>
+          <t>-7,46; 144,48</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-24,79; 105,91</t>
+          <t>-26,65; 109,68</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-20,62; 118,46</t>
+          <t>-16,0; 117,42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-56,1; 28,76</t>
+          <t>-58,3; 25,08</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-57,97; 32,56</t>
+          <t>-56,53; 33,34</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-60,88; 44,06</t>
+          <t>-19,18; 88,34</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-24,29; 55,03</t>
+          <t>-21,25; 54,82</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-32,85; 46,66</t>
+          <t>-30,2; 43,6</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-37,89; 52,95</t>
+          <t>-5,58; 75,71</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-1,27</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>0,11</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,84; -0,46</t>
+          <t>-4,9; -0,42</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 3,4</t>
+          <t>-1,34; 3,38</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 1,16</t>
+          <t>-1,92; 2,47</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,33; -0,05</t>
+          <t>-4,39; 0,13</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,54</t>
+          <t>-2,91; 1,99</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 2,36</t>
+          <t>-2,09; 2,27</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,88; -0,84</t>
+          <t>-3,96; -0,96</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,94</t>
+          <t>-1,52; 1,85</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,1</t>
+          <t>-1,34; 1,65</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-22,0%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-10,72%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-68,97; -8,8</t>
+          <t>-68,32; -7,9</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 75,3</t>
+          <t>-19,84; 70,14</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-66,9; 23,81</t>
+          <t>-28,25; 54,03</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-62,44; 1,44</t>
+          <t>-62,22; 5,88</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-44,12; 35,01</t>
+          <t>-42,35; 46,64</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-27,46; 55,94</t>
+          <t>-29,08; 51,85</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-59,03; -15,38</t>
+          <t>-60,13; -19,65</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-24,72; 40,25</t>
+          <t>-23,19; 38,4</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-47,06; 20,76</t>
+          <t>-21,13; 34,21</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>0,2</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,04</t>
+          <t>-1,28; 1,0</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,59</t>
+          <t>-0,63; 1,66</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,07</t>
+          <t>-0,75; 1,34</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,61</t>
+          <t>-1,6; 0,55</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,26</t>
+          <t>-1,08; 1,2</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,57</t>
+          <t>-1,02; 0,94</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,46</t>
+          <t>-1,0; 0,49</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,11</t>
+          <t>-0,42; 1,16</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,64</t>
+          <t>-0,53; 0,94</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-0,36%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-7,3%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-3,9%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 21,89</t>
+          <t>-21,4; 20,51</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 32,54</t>
+          <t>-10,59; 33,57</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-27,05; 21,93</t>
+          <t>-12,14; 27,12</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-26,0; 13,5</t>
+          <t>-27,38; 11,94</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 26,76</t>
+          <t>-18,71; 24,56</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-27,0; 12,23</t>
+          <t>-16,84; 19,6</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 9,24</t>
+          <t>-17,56; 9,7</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 22,24</t>
+          <t>-7,41; 22,92</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 12,94</t>
+          <t>-9,27; 19,29</t>
         </is>
       </c>
     </row>
